--- a/data_execl/base_data/LuxuryFund.xlsx
+++ b/data_execl/base_data/LuxuryFund.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F39" s="0" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F41" s="0" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F43" s="0" t="n">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F44" s="0" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F46" s="0" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F48" s="0" t="n">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F49" s="0" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F51" s="0" t="n">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F53" s="0" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F54" s="0" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F56" s="0" t="n">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F58" s="0" t="n">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F59" s="0" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F61" s="0" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F63" s="0" t="n">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F64" s="0" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
-          <t>16#2080</t>
+          <t>16#2540</t>
         </is>
       </c>
       <c r="F66" s="0" t="n">
